--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/NORTH_CAROLINA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/NORTH_CAROLINA_2012.xlsx
@@ -3624,7 +3624,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C182">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C210">
@@ -13830,7 +13830,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C749">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C899">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C900">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="B958" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C958">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C959">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C965">
@@ -25602,7 +25602,7 @@
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1403">
@@ -26070,7 +26070,7 @@
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1429">
@@ -28968,7 +28968,7 @@
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1590">
